--- a/RefractionApp/Refraction/Resources/SampleData/time_series.xlsx
+++ b/RefractionApp/Refraction/Resources/SampleData/time_series.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,98 +438,76 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.86</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="n">
-        <v>2.05</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>5.63</v>
+        <v>4.8</v>
       </c>
       <c r="C4" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>6.95</v>
+        <v>7.5</v>
       </c>
       <c r="C5" t="n">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
-        <v>5.9</v>
+        <v>10.2</v>
       </c>
       <c r="C6" t="n">
-        <v>4.24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B7" t="n">
-        <v>8.77</v>
+        <v>12.8</v>
       </c>
       <c r="C7" t="n">
-        <v>6.03</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>11.53</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>5.67</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B9" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="C9" t="n">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>24</v>
-      </c>
-      <c r="B10" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="C10" t="n">
-        <v>8.02</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>
